--- a/digital-products/excel-source/CashFlowOffice_SubVendorManager_v1.xlsx
+++ b/digital-products/excel-source/CashFlowOffice_SubVendorManager_v1.xlsx
@@ -959,7 +959,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1266,6 +1266,10 @@
     </xf>
     <xf numFmtId="164" fontId="19" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3888,7 +3892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -3957,7 +3961,7 @@
       <c r="A3" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="36" t="n">
+      <c r="B3" s="77" t="n">
         <f aca="true">TODAY()</f>
         <v>46111</v>
       </c>
@@ -5614,7 +5618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -5670,7 +5674,7 @@
       <c r="A3" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="36" t="n">
+      <c r="B3" s="77" t="n">
         <f aca="true">TODAY()</f>
         <v>46111</v>
       </c>
@@ -9985,7 +9989,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -10038,7 +10042,7 @@
       <c r="A3" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="36" t="n">
+      <c r="B3" s="77" t="n">
         <f aca="true">TODAY()</f>
         <v>46111</v>
       </c>
